--- a/analyse_bacot_complet.xlsx
+++ b/analyse_bacot_complet.xlsx
@@ -2023,25 +2023,23 @@
       </c>
       <c r="B7" s="77" t="inlineStr">
         <is>
-          <t>💬 Commentaire</t>
-        </is>
-      </c>
-      <c r="C7" s="77" t="inlineStr">
-        <is>
-          <t>YouTube — Tibo InShape</t>
-        </is>
-      </c>
+          <t>📰 Article</t>
+        </is>
+      </c>
+      <c r="C7" s="77" t="inlineStr"/>
       <c r="D7" s="76" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="E7" s="76" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F7" s="78" t="inlineStr">
         <is>
-          <t>« Je comprends totalement qu'elle s'en veuille de l'avoir tué, c'est normal, ça aurait dû être le rôle de l'état de la protéger et c'est un acte impardonnable. Pourtant, je pense qu'on a tous compris à quel point il y avait injustice, et à quel point elle était en danger. Certes l'acte n'aurait pas dû être celui-là, mais on comprend tous à quel point elle n'avait pas le choix, et à quel point la pulsion de tirer a été à la fois une faiblesse et une force. Je comprends q ... »</t>
+          <t>« ... De plus, dans certaines régions, départements et même certains arrondissements de Paris, il n’y a pas toujours de psychiatres dans les unités médico-judiciaires. Or seuls les psychiatres peuvent évaluer une ITT dans le cadre de violence psychologique… J’observe cela dans un cas sur quatre.
+Le droit français sur ce sujet vous paraît-il adapté ? Doit-il évoluer ?
+J’estime que le Code pénal ne répond pas aux exigences souhaitables pour suffisamment protéger les femmes victimes de violences conjuga ... »</t>
         </is>
       </c>
     </row>
@@ -2051,22 +2049,27 @@
       </c>
       <c r="B8" s="77" t="inlineStr">
         <is>
-          <t>📰 Article</t>
-        </is>
-      </c>
-      <c r="C8" s="77" t="inlineStr"/>
+          <t>💬 Commentaire</t>
+        </is>
+      </c>
+      <c r="C8" s="77" t="inlineStr">
+        <is>
+          <t>YouTube — RTS - Radio Télévision Suisse</t>
+        </is>
+      </c>
       <c r="D8" s="76" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="E8" s="76" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F8" s="78" t="inlineStr">
         <is>
-          <t>« ... "Il faut que la société prenne réellement conscience de la dangerosité des hommes violents, et donc de la nécessité de protéger." Sur ce plan, poursuit-elle, "on voit qu'il y a des progrès, mais on voit aussi que les failles restent très importantes... Et pour l'instant, on n'a pas fini de penser la dangerosité."
-Et Ernestine Ronai de conclure : "Il faut qu'on entende mieux la parole des victimes, qu'on croit mieux les victimes et donc qu'on »</t>
+          <t>« ... bilisé", il va agir comme un baume psychique et restituer UNIQUEMENT les affects positifs qu'éprouvaient la victime AVANT le premier choc psychique provoqué verbalement ou physiquement. Le cerveau trompe la victime sur la réalité. C'est dramatique pour les victimes. 
+Le cerveau va pouvoir enregistrer, à nouveau, normalement, et se "détendre" qu'en période accalmie. La période où l'agresseur culpabilise la victime et minimise les faits. 
+Malheureusement, c'est ce que la victime va retenir, répét ... »</t>
         </is>
       </c>
     </row>
@@ -2076,23 +2079,26 @@
       </c>
       <c r="B9" s="77" t="inlineStr">
         <is>
-          <t>📰 Article</t>
-        </is>
-      </c>
-      <c r="C9" s="77" t="inlineStr"/>
+          <t>💬 Commentaire</t>
+        </is>
+      </c>
+      <c r="C9" s="77" t="inlineStr">
+        <is>
+          <t>YouTube — CNEWS</t>
+        </is>
+      </c>
       <c r="D9" s="76" t="inlineStr">
         <is>
-          <t>2021-11-22</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="E9" s="76" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F9" s="78" t="inlineStr">
         <is>
-          <t>« ... ui ont concerné 159.400 personnes tous sexes confondus en 2020, a annoncé ce lundi 22 novembre le service statistiques du ministère de l’Intérieur.
-Environ 87% des victimes de violences conjugales sont des femmes, soit 139.200, une proportion stable par rapport à 2019 (125.840 femmes pour 142.310 victimes), selon ces chiffres du ministère, qui ne comptabilisent pas les homicides.
-En 2020, 102 femmes avaient été tuées sous les coups de leur conjoint ou ex. Elles étaient 146 en 2019. Les victimes ... »</t>
+          <t>« ... On ne se fait pas justice soi même, c'est dur à comprendre mais on est plus au moyen âge, et oui, dommage. De plus, qu'en savez vous de la justice ? Sur une affaire que vous ne comprenez pas la justice est nulle et merdique ? Parlez moi de vices de procédures à la limite j'aurais compris pourquoi vous dénoncez de cette façon la justice ! 
+Je n'ai pas l'esprit procédurier du tout, vous ne me connaissez pas. Je ne dis ABSOLUMENT PAS que le mari est une victime, si vous préférez que j' ... »</t>
         </is>
       </c>
     </row>
@@ -2107,20 +2113,26 @@
       </c>
       <c r="C10" s="77" t="inlineStr">
         <is>
-          <t>YouTube — Bercrimes</t>
+          <t>YouTube — Pluriel</t>
         </is>
       </c>
       <c r="D10" s="76" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="E10" s="76" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F10" s="78" t="inlineStr">
         <is>
-          <t>« ... A chaque feminicide,  la question est posée : est ce qu'on aurait pû l'éviter ? Et à chaque fois, même constat, la réponse est oui. Si Valérie n'avait pas eu ce réflexe,  elle ferait partie des victimes, et se serait ajoutée à la longue liste des chiffres concernant les féminicides. J'estime qu'elle n'a rien à faire aux assises déjà. Courage à elle qui a trop subit,  elle doit être reconnue comme une victime et non une m »</t>
+          <t>« ... e chapeau et sest fait 
+Passe lui le pauvre pour la victime ..et a berne ces juges qui sûrement venaient de debuter leur metier pour en conclure a une condamnation nulle et classe aux oubliettes .
+Aberrant ,humiliant ,abominables pour les victimes ,plus que ce qu'elles ont en fait deja subi .
+La justice sert a quoi au final 
+Donner raisons aux délinquants et ignores la souffrance de ces pauvres femmes sous lemprise de leurs bourreaux !!!
+Complément ahurrissant ,revoltant !
+Courage a vous et s ... »</t>
         </is>
       </c>
     </row>
@@ -2130,23 +2142,25 @@
       </c>
       <c r="B11" s="77" t="inlineStr">
         <is>
-          <t>📰 Article</t>
-        </is>
-      </c>
-      <c r="C11" s="77" t="inlineStr"/>
+          <t>💬 Commentaire</t>
+        </is>
+      </c>
+      <c r="C11" s="77" t="inlineStr">
+        <is>
+          <t>YouTube — Tibo InShape</t>
+        </is>
+      </c>
       <c r="D11" s="76" t="inlineStr">
         <is>
-          <t>2022-07-04</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="E11" s="76" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F11" s="78" t="inlineStr">
         <is>
-          <t>« ... e justice auprès de sa fille de 5 ans, qu’il voit pourtant comme un père normal qu’il n’est pourtant pas.”
-“Il continuera de croire qu’il est en mesure de faire pression sur moi et de me harceler moralement. Je n’en peux plus. J’exige d’avoir la paix. C’est plus clair comme ça?”, conclut-elle.
-Un message choc qui a très vite suscité de nombreuses réactions. Parmi lesquelles celles de plusieurs personnalités qui ont manifesté leur soutien à la comédienne de 37 ans. “Tu as tout mon soutien. Quel e ... »</t>
+          <t>« Je comprends totalement qu'elle s'en veuille de l'avoir tué, c'est normal, ça aurait dû être le rôle de l'état de la protéger et c'est un acte impardonnable. Pourtant, je pense qu'on a tous compris à quel point il y avait injustice, et à quel point elle était en danger. Certes l'acte n'aurait pas dû être celui-là, mais on comprend tous à quel point elle n'avait pas le choix, et à quel point la pulsion de tirer a été à la fois une faiblesse et une force. Je comprends q ... »</t>
         </is>
       </c>
     </row>
@@ -2196,19 +2210,77 @@
       </c>
       <c r="B16" s="80" t="inlineStr">
         <is>
+          <t>💬 Commentaire</t>
+        </is>
+      </c>
+      <c r="C16" s="80" t="inlineStr">
+        <is>
+          <t>YouTube — AFP</t>
+        </is>
+      </c>
+      <c r="D16" s="79" t="inlineStr">
+        <is>
+          <t>2021-06-23</t>
+        </is>
+      </c>
+      <c r="E16" s="79" t="n">
+        <v>14</v>
+      </c>
+      <c r="F16" s="78" t="inlineStr">
+        <is>
+          <t>« Elle mérite d'être condamnée car elle a commis un assassinat, sans même avoir essayé de faire appel à la police.
+Mais si elle l'a fait, c'est notamment parce qu'elle était sous emprise, isolée par son bourreau, et que dans cette situation d'isolement elle avait le sentiment qu'il n'y avait pas d'autre solution.
+Et on ne peut s'empêcher de penser à l'affaire Mannechez dans laquelle Virginie Mannechez avait, elle, fait appel à la police et à des associations pour l ... »</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="100" customHeight="1" s="61">
+      <c r="A17" s="79" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="80" t="inlineStr">
+        <is>
+          <t>💬 Commentaire</t>
+        </is>
+      </c>
+      <c r="C17" s="80" t="inlineStr">
+        <is>
+          <t>YouTube — HugoDécrypte - Actus du jour</t>
+        </is>
+      </c>
+      <c r="D17" s="79" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="E17" s="79" t="n">
+        <v>12</v>
+      </c>
+      <c r="F17" s="78" t="inlineStr">
+        <is>
+          <t>« ... Mais si t'as des emmerdes avec la police, je suis prêt à parier que ta couleur de peau ou que tes origines n'ont rien à voir avec ça, mais que tu as plutôt tendance à être tendre avec la police, ou à être dans certaines choses très légales. Et si t'as aucune embrouille avec eux, je suppose que t'as rien à te reprocher. J'ai jamais eu la moindre embrouille avec la police. Pourquoi à ton avi ? Parce que je suis ... »</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="100" customHeight="1" s="61">
+      <c r="A18" s="79" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="80" t="inlineStr">
+        <is>
           <t>📰 Article</t>
         </is>
       </c>
-      <c r="C16" s="80" t="inlineStr"/>
-      <c r="D16" s="79" t="inlineStr">
+      <c r="C18" s="80" t="inlineStr"/>
+      <c r="D18" s="79" t="inlineStr">
         <is>
           <t>2021-06-25</t>
         </is>
       </c>
-      <c r="E16" s="79" t="n">
+      <c r="E18" s="79" t="n">
         <v>10</v>
       </c>
-      <c r="F16" s="78" t="inlineStr">
+      <c r="F18" s="78" t="inlineStr">
         <is>
           <t>« clamé jeudi une condamnation pour l'exemple, mais sans exiger de peine précise, à l'encontre de Valérie Bacot, jugée pour
 - l'assassinat de son mari violent et proxénète.
@@ -2216,29 +2288,29 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="100" customHeight="1" s="61">
-      <c r="A17" s="79" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="80" t="inlineStr">
+    <row r="19" ht="100" customHeight="1" s="61">
+      <c r="A19" s="79" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="80" t="inlineStr">
         <is>
           <t>💬 Commentaire</t>
         </is>
       </c>
-      <c r="C17" s="80" t="inlineStr">
+      <c r="C19" s="80" t="inlineStr">
         <is>
           <t>YouTube — Europe 1</t>
         </is>
       </c>
-      <c r="D17" s="79" t="inlineStr">
+      <c r="D19" s="79" t="inlineStr">
         <is>
           <t>2021-06-23</t>
         </is>
       </c>
-      <c r="E17" s="79" t="n">
+      <c r="E19" s="79" t="n">
         <v>10</v>
       </c>
-      <c r="F17" s="78" t="inlineStr">
+      <c r="F19" s="78" t="inlineStr">
         <is>
           <t>« ... Il avait pris un an de prison ferme, parce qu'il y avait eu meurtre mais que les jurés ont largement pris en compte les circonstances atténuantes.
 Une condamnation similaire apparaîtrait juste dans le cas présent, même si elle mériterait plus car il y a assassinat et non meurtre, et que contrairement au cas précédent il n'y avait pas de risque vital immédiat...
@@ -2246,85 +2318,33 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="100" customHeight="1" s="61">
-      <c r="A18" s="79" t="n">
-        <v>3</v>
-      </c>
-      <c r="B18" s="80" t="inlineStr">
-        <is>
-          <t>💬 Commentaire</t>
-        </is>
-      </c>
-      <c r="C18" s="80" t="inlineStr">
-        <is>
-          <t>YouTube — Le Point</t>
-        </is>
-      </c>
-      <c r="D18" s="79" t="inlineStr">
-        <is>
-          <t>2021-06-23</t>
-        </is>
-      </c>
-      <c r="E18" s="79" t="n">
-        <v>8</v>
-      </c>
-      <c r="F18" s="78" t="inlineStr">
-        <is>
-          <t>« ... On ne règle pas ses problèmes à coups de fusil sans passer par la justice et la police au préalable.
-Quant à l'affaire SAUVAGE, je rappellerais qu'elle avait été jugée deux fois par un jury populaire et condamnée deux fois par des gens ordinaires à 10 ans. Cette peine était justifiée car sa version ne tenait pas la route. Elle prétendait être battue par son mari mais lorsque celui-ci lui annonça q ... »</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="100" customHeight="1" s="61">
-      <c r="A19" s="79" t="n">
-        <v>4</v>
-      </c>
-      <c r="B19" s="80" t="inlineStr">
-        <is>
-          <t>📰 Article</t>
-        </is>
-      </c>
-      <c r="C19" s="80" t="inlineStr"/>
-      <c r="D19" s="79" t="inlineStr">
-        <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="E19" s="79" t="n">
-        <v>8</v>
-      </c>
-      <c r="F19" s="78" t="inlineStr">
-        <is>
-          <t>« ... "C'est elle qui voulait", assure la mère. "Mais qu'est-ce qui vous est passé par la tête?", crie l'avocate. "Je n'ai rien imposé", affirme Joëlle Aubague.
-La mère restera sans mots quand l'avocate lui annoncera que sa fille vient de déposer plainte contre elle pour "complicité de viol par omission".
-Daniel Polette décrit comme "le diable"
-"Je voudrais bien pouvoir faire marche arrière", lâche la mère, concédant ne pas avoir été "parfaite" mais assurant n'avoir jamais ... »</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="100" customHeight="1" s="61">
       <c r="A20" s="79" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="80" t="inlineStr">
         <is>
-          <t>📰 Article</t>
-        </is>
-      </c>
-      <c r="C20" s="80" t="inlineStr"/>
+          <t>💬 Commentaire</t>
+        </is>
+      </c>
+      <c r="C20" s="80" t="inlineStr">
+        <is>
+          <t>YouTube — BFMTV</t>
+        </is>
+      </c>
       <c r="D20" s="79" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2021-06-27</t>
         </is>
       </c>
       <c r="E20" s="79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20" s="78" t="inlineStr">
         <is>
-          <t>« Procès de Valérie Bacot : une condamnation "pour l'exemple", elle fait un malaise
-La partie civile a réclamé jeudi une condamnation pour l'exemple, mais sans exiger de peine précise, à l'encontre de Valérie Bacot, jugée pour l'assassinat de son mari violent et proxénète.
-Depuis lundi, Valérie Bacot est jugée devant les Assises de Saône-et-Loire à Chalon-sur-Saône pour l'assassinat de son mari Daniel Polette. Au quatrième jour du procès, jeudi, dans sa plaidoirie, Béatrice Saggio qui défend les i ... »</t>
+          <t>« @laurine7704 Désolé, mais c'est simplement factuel. Le tribunal l'a reconnue comme assassin.
+C'est pas une insulte de dire ça. Mais un meurtre avec préméditation est par définition un assassinat. Même si la victime est une ordure.
+Si quelqu'un avait tué Hitler avec préméditation, il aurait été un assassin. Et pourtant un héros. »</t>
         </is>
       </c>
     </row>
@@ -2334,25 +2354,29 @@
       </c>
       <c r="B21" s="80" t="inlineStr">
         <is>
-          <t>📰 Article</t>
-        </is>
-      </c>
-      <c r="C21" s="80" t="inlineStr"/>
+          <t>💬 Commentaire</t>
+        </is>
+      </c>
+      <c r="C21" s="80" t="inlineStr">
+        <is>
+          <t>YouTube — Immersion ▸ reportages et docu</t>
+        </is>
+      </c>
       <c r="D21" s="79" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="E21" s="79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F21" s="78" t="inlineStr">
         <is>
-          <t>« ... Les trois victimes "transportées à l'hôpital"
-Les forces de l'ordre ont précisé que "les motivations de l'agression font l'objet d'une enquête"
-. "Les trois victimes, de nationalité suisse, sont âgées de 28, 43 et 52 ans. Elles ont toutes été transportées à l'hôpital"
-, a poursuivi la police, sans indication sur la gravité de leurs blessures.
-"En collaboration avec la police cantonale de Zurich, la police municipale de Winterthour ... »</t>
+          <t>« ... Je prends la voiture sous l'emprise de l'alcool ou de stupéfiants, je conduis =&gt; je connais le risque, je sais qu'à tout moment, mes réflexes ne sont pas à 100% et je peux tuer quelqu'un.
+J'ai une arme chargée, je menace pour faire peur =&gt; je connais le risque de faire une mauvaise manipulation et de pouvoir tuer quelqu'un.
+Ect... Ect...
+Sauf en cas de légitime défense, cette nuance visant à invoquer une préméditation ou non ne devrait même pas exister.
+A partir du moment où je prend »</t>
         </is>
       </c>
     </row>
@@ -2459,13 +2483,64 @@
       <c r="C28" s="82" t="inlineStr"/>
       <c r="D28" s="81" t="inlineStr">
         <is>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="E28" s="81" t="n">
+        <v>22</v>
+      </c>
+      <c r="F28" s="78" t="inlineStr">
+        <is>
+          <t>« même combat ?
+Alexandra Lange, acquittée en 2012
+Elle a tué son mari d’un coup de couteau à la gorge, dans la nuit du 18 au 19 juin 2009 à Douai. Trois ans plus tard, la cour d’assises du Nord l’acquittait, reconnaissant la légitime défense. L’avocat général Luc Frémiot, magistrat chargé de porter l’accusation, avait lui-même requis un acquittement pour une femme « que la société n’a pas su protéger », après plus d’un ... »</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="100" customHeight="1" s="61">
+      <c r="A29" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" s="82" t="inlineStr">
+        <is>
+          <t>📰 Article</t>
+        </is>
+      </c>
+      <c r="C29" s="82" t="inlineStr"/>
+      <c r="D29" s="81" t="inlineStr">
+        <is>
+          <t>2021-01-22</t>
+        </is>
+      </c>
+      <c r="E29" s="81" t="n">
+        <v>22</v>
+      </c>
+      <c r="F29" s="78" t="inlineStr">
+        <is>
+          <t>« ... Lequel parle aussi de « syndrome de la femme battue ». « C’est la première fois que cette notion, qui nous vient du Canada , est ainsi évoquée. Elle doit permettre d’introduire l’idée de légitime défense différée : on peut considérer que s’il y a violence, c’est qu’il y a danger, précise la sénatrice. Nous pouvons aller plus loin que l’article 122-5 du Code pénal relatif à cette légitime défense. »
+La prudence du garde des S ... »</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="100" customHeight="1" s="61">
+      <c r="A30" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="82" t="inlineStr">
+        <is>
+          <t>📰 Article</t>
+        </is>
+      </c>
+      <c r="C30" s="82" t="inlineStr"/>
+      <c r="D30" s="81" t="inlineStr">
+        <is>
           <t>2024-01-16</t>
         </is>
       </c>
-      <c r="E28" s="81" t="n">
+      <c r="E30" s="81" t="n">
         <v>21</v>
       </c>
-      <c r="F28" s="78" t="inlineStr">
+      <c r="F30" s="78" t="inlineStr">
         <is>
           <t>« ... Malgré tout, la peine est confirmée en appel, en 2015.
 Aussitôt, la condamnation de Jacqueline Sauvage suscite l'incompréhension générale. L'affaire devient médiatique et face à la mobilisation, François Hollande accorde une grâce totale à Jacqueline Sauvage en décembre 2016, après le rejet d'une grâce partielle. Aujourd'hui décédée, Jacqueline Sauvage reste une figure symbolique de la lutte contre les violences faites aux femmes.
@@ -2473,25 +2548,25 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="100" customHeight="1" s="61">
-      <c r="A29" s="81" t="n">
-        <v>4</v>
-      </c>
-      <c r="B29" s="82" t="inlineStr">
+    <row r="31" ht="100" customHeight="1" s="61">
+      <c r="A31" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" s="82" t="inlineStr">
         <is>
           <t>📰 Article</t>
         </is>
       </c>
-      <c r="C29" s="82" t="inlineStr"/>
-      <c r="D29" s="81" t="inlineStr">
+      <c r="C31" s="82" t="inlineStr"/>
+      <c r="D31" s="81" t="inlineStr">
         <is>
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="E29" s="81" t="n">
+      <c r="E31" s="81" t="n">
         <v>18</v>
       </c>
-      <c r="F29" s="78" t="inlineStr">
+      <c r="F31" s="78" t="inlineStr">
         <is>
           <t>« ... RETOUR SUR L’AFFAIRE DE LA CLAYETTE
 Surnommée “La nouvelle Jacqueline Sauvage”, Valérie Bacot a fait la une des journaux après avoir été accusée et arrêtée du meurtre de son conjoint, Daniel Polette, le 2 octobre 2017.
@@ -2500,58 +2575,6 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="100" customHeight="1" s="61">
-      <c r="A30" s="81" t="n">
-        <v>5</v>
-      </c>
-      <c r="B30" s="82" t="inlineStr">
-        <is>
-          <t>📰 Article</t>
-        </is>
-      </c>
-      <c r="C30" s="82" t="inlineStr"/>
-      <c r="D30" s="81" t="inlineStr">
-        <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="E30" s="81" t="n">
-        <v>15</v>
-      </c>
-      <c r="F30" s="78" t="inlineStr">
-        <is>
-          <t>« ... En médiatisant ses affaires (Alexandra Lange, Jacqueline Sauvage, Valérie Bacot), l’avocate tente de faire progresser le droit et d’y introduire de nouveaux concepts reconnus ailleurs pour faire avancer la cause des femmes.
-Comment tentez-vous de faire évoluer la justice malgré des textes restrictifs ?
-J’ai commencé avec l’affaire Jacqueline Sauvage, où j’ai expliqué que la définition du Code pénal de la légitime défense n’était absolument pas ada ... »</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="100" customHeight="1" s="61">
-      <c r="A31" s="81" t="n">
-        <v>6</v>
-      </c>
-      <c r="B31" s="82" t="inlineStr">
-        <is>
-          <t>📰 Article</t>
-        </is>
-      </c>
-      <c r="C31" s="82" t="inlineStr"/>
-      <c r="D31" s="81" t="inlineStr">
-        <is>
-          <t>2021-06-27</t>
-        </is>
-      </c>
-      <c r="E31" s="81" t="n">
-        <v>13</v>
-      </c>
-      <c r="F31" s="78" t="inlineStr">
-        <is>
-          <t>« ... Vers la reconnaissance du syndrome de la femme battue ?
-Devant les jurés, l’avocate a fait référence à un amendement adopté en juin par le Sénat dans une proposition de loi sur l’irresponsabilité pénale. Le but de cet amendement, voté à ce stade en première lecture et qui suscite l’opposition du ministère de la justice, vise à faire reconnaître dans la loi française le syndrome de la femme battue (SFB) validé en 1990 par la Cour suprême du Canada.
-→ REPORTA ... »</t>
-        </is>
-      </c>
-    </row>
     <row r="32" ht="8" customHeight="1" s="61"/>
     <row r="34" ht="32" customHeight="1" s="61">
       <c r="A34" s="74" t="inlineStr">
@@ -2604,17 +2627,15 @@
       <c r="C36" s="84" t="inlineStr"/>
       <c r="D36" s="83" t="inlineStr">
         <is>
-          <t>2022-03-08</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="E36" s="83" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="F36" s="78" t="inlineStr">
         <is>
-          <t>« ... Le féminicide, l'ultime violence faite aux femmes
-"Toutes les violences contre les femmes sont sous-tendues par les mêmes mécanismes et les mêmes enjeux : les stéréotypes et la domination masculine", développe la porte-parole d'Osez le Féminisme. De toutes ces violences - "sexisme ordinaire, harcèlement de rue, agressions sexuelles, viols, inégalités professionnelles..."- le féminicide en est l'apogée. L'ultime violence faite aux femmes.
-No ... »</t>
+          <t>« ... st très intéressante : évoquer un féminicide non intime permettrait de mettre le genre de la victime au centre des débats et des tentatives de comprendre le crime. Si l’Espagne a fait tant de progrès dans la lutte contre les violences faites aux femmes, c’est, en partie, en nommant les choses correctement : dans le langage courant, les Espagnols parlent de « crime machiste » pour des meurtres de femmes, que la victime soit ou pas la conjointe de l’auteur. Cela rejoint la notion de « féminicide n ... »</t>
         </is>
       </c>
     </row>
@@ -2630,15 +2651,15 @@
       <c r="C37" s="84" t="inlineStr"/>
       <c r="D37" s="83" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="E37" s="83" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F37" s="78" t="inlineStr">
         <is>
-          <t>« ... st très intéressante : évoquer un féminicide non intime permettrait de mettre le genre de la victime au centre des débats et des tentatives de comprendre le crime. Si l’Espagne a fait tant de progrès dans la lutte contre les violences faites aux femmes, c’est, en partie, en nommant les choses correctement : dans le langage courant, les Espagnols parlent de « crime machiste » pour des meurtres de femmes, que la victime soit ou pas la conjointe de l’auteur. Cela rejoint la notion de « féminicide n ... »</t>
+          <t>« ... inimum pour une prise en charge de qualité des femmes victimes de violences conjugales » serait à lui seul d’environ « 506 millions d’euros », dans l’hypothèse la plus basse, et de « 1,1 milliard », dans l’hypothèse la plus haute, ont estimé, dans leur rapport de 2018 faisant suite au Grenelle contre les violences faites aux femmes, les cinq organisations suivantes : le Conseil économique social et environnemental, le Haut conseil pour l’égalité, la Fondation des femmes, le Fonds pour les femmes »</t>
         </is>
       </c>
     </row>
@@ -2653,22 +2674,22 @@
       </c>
       <c r="C38" s="84" t="inlineStr">
         <is>
-          <t>YouTube — Public Sénat</t>
+          <t>YouTube — Les Couilles sur la table</t>
         </is>
       </c>
       <c r="D38" s="83" t="inlineStr">
         <is>
-          <t>2021-11-05</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="E38" s="83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F38" s="78" t="inlineStr">
         <is>
-          <t>« Je ne pense pas que ce soit une domination patriarcale comme le dit Mme Cohen à la fin de son intervention mais bien une domination de *certains* hommes envers des femmes.
-L'amalgame est certes facile, de son point de vue, puisqu'elle considère que les lois, ds leurs ensembles, sont faites par des hommes et pour des hommes (???) elle le dit d'ailleurs précédemment en utilisant le terme "d'angle mort" concernant les violences faites aux femmes comme aux enfants.
-Or, il me semble qu'une victime r ... »</t>
+          <t>« ... dans la psychanalyse, j'ai esquivé le chemin tout tracé en abordant la violence conjugale dans les couples gay.
+Tout d'un coup, parler de violence conjugale entre 2 hommes ou entre 2 femmes permettait de parler de la violence en tant que telle, et de sortir de cette question qui taraude particulièrement la société française : les rapports entre genres...
+Entre deux personnes de même sexe, la violence conjugale peut être abordée de manière systémique : la systémique, c'est justement de là que vie ... »</t>
         </is>
       </c>
     </row>
@@ -2678,22 +2699,28 @@
       </c>
       <c r="B39" s="84" t="inlineStr">
         <is>
-          <t>📰 Article</t>
-        </is>
-      </c>
-      <c r="C39" s="84" t="inlineStr"/>
+          <t>💬 Commentaire</t>
+        </is>
+      </c>
+      <c r="C39" s="84" t="inlineStr">
+        <is>
+          <t>YouTube — Pluriel</t>
+        </is>
+      </c>
       <c r="D39" s="83" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E39" s="83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F39" s="78" t="inlineStr">
         <is>
-          <t>« ... Lire aussi &gt;&gt; Le procès de Valérie Bacot, Jour 1, Jour 2, Jour 3
-Comme dans toutes les affaires de violences conjugales, la notion d’emprise est cette fois encore au cœur des débats. Élevée dans un foyer où le père, souvent absent, et la mère, défaillante, divorcent par deux fois, « Valérie Bacot a grandi dans une carence affective et éducative précoce », souligne Denis Prieur, psychiatre expert auprès de la cour d’appel de Dijon. Les repères fondamentaux structurels font défaut. Il n’y ... »</t>
+          <t>« e violences conjugales au cas où, sous emprise psychologique et physique et matérielle également, être là c’est genre la moindre des choses quand on est réellement amis.
+Je suis d’accord avec le fait de dire clairement les choses, mais au vu du contexte votre commentaire c’est juste un manque d’empathie.
+Donc elle devait se débrouiller seule ? Surtout aussi jeune ? Se replier sur soi même pour pas bousculer les autres dans leurs petites vies?
+Comme elle dit ce genre de situation ne sont pas bina »</t>
         </is>
       </c>
     </row>
@@ -2703,26 +2730,27 @@
       </c>
       <c r="B40" s="84" t="inlineStr">
         <is>
-          <t>📰 Article</t>
-        </is>
-      </c>
-      <c r="C40" s="84" t="inlineStr"/>
+          <t>💬 Commentaire</t>
+        </is>
+      </c>
+      <c r="C40" s="84" t="inlineStr">
+        <is>
+          <t>YouTube — Esprit de justice</t>
+        </is>
+      </c>
       <c r="D40" s="83" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="E40" s="83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" s="78" t="inlineStr">
         <is>
-          <t>« ... t souvenus d’un autre drame, survenu quatre ans plus tôt dans la même maison : la mort de Maryline Deschatres, précédente compagne de Serge Bacot.
-En 2017, la jeune femme de 38 ans était décédée après une chute dans l’escalier.
-L’enquête avait alors conclu à un accident, conclusion remise en cause après le drame de 2021.
-En février 2023, Serge Bacot était mis en examen une deuxième fois dans cette affaire.
-L’accusé nie les faits depuis le début
-C’est donc pour deux homicides, deux féminicides, q ... »</t>
+          <t>« Une femme qui ment peu importe la raison; ne morfle jamais y compris devant un juge, c'est quand même hyper terrifiant cette impunité systématique.
+La juge visiblement déçue avait déjà son verdict en tête (c'est d'ailleurs très contestable qu'une femme nécessairement de parti pris arbitraire, juge en toute partialité ce genre d'affaire... c'est même en vérité absolue; parfaitement scandaleux...)
+L'emprise... Un terme à la mode qui permet de décharger une femme de sa responsabilité à entretenir ... »</t>
         </is>
       </c>
     </row>
@@ -2737,20 +2765,20 @@
       </c>
       <c r="C41" s="84" t="inlineStr">
         <is>
-          <t>YouTube — ALIBI. ▸ faits divers</t>
+          <t>YouTube — AJ+ français</t>
         </is>
       </c>
       <c r="D41" s="83" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E41" s="83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F41" s="78" t="inlineStr">
         <is>
-          <t>« C'est toujours la faute des flics qu'est-ce que vous voulez les gendarmes ils font ce qu'ils peuvent et et après il nous parle de sous emprise sous emprise y en a marre marre qu'est-ce qu'il faut faire »</t>
+          <t>« ​@HellineD attention il ne parle pas de féministe il parle de féministe extrémiste c'est très différent les féministes veulent légalité les féministes extrémistes veulent écraser les hommes jusqu'au dernier »</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2842,8 @@
       </c>
       <c r="F46" s="78" t="inlineStr">
         <is>
-          <t>« ... t "soumise à l'emprise totalitaire de ce tyran domestique" qui l'a violée dès l'âge de 12-13 ans, quand il était encore son beau-père. Elle s'est "trouvée enfermée, emprisonnée dans l'emprise de son mari totalitaire". Une emprise "dominante" et surtout "permanente", explique l'expert. "Elle n'avait plus réellement de libre arbitre: elle a peur car son mari était toujours dans sa tête. Elle était toujours terrorisée et restait avec les diktats de son mari. L'emprise est permanente, pas seulement ... »</t>
+          <t>« ... umise à l'emprise totalitaire de ce tyran domestique » qui l'a violée dès l'âge de 12-13 ans, quand il était encore son beau-père. Elle s'est « trouvée enfermée, emprisonnée dans l'emprise de son mari totalitaire ». Une emprise « dominante » et surtout « permanente », explique l'expert.
+« Elle n'avait plus réellement de libre arbitre : elle a peur, car son mari était toujours dans sa tête. Elle était toujours terrorisée et restait avec les diktats de son mari. L'emprise est permanente, pas seule ... »</t>
         </is>
       </c>
     </row>
@@ -2834,9 +2863,33 @@
         </is>
       </c>
       <c r="E47" s="85" t="n">
+        <v>15</v>
+      </c>
+      <c r="F47" s="78" t="inlineStr">
+        <is>
+          <t>« ... t "soumise à l'emprise totalitaire de ce tyran domestique" qui l'a violée dès l'âge de 12-13 ans, quand il était encore son beau-père. Elle s'est "trouvée enfermée, emprisonnée dans l'emprise de son mari totalitaire". Une emprise "dominante" et surtout "permanente", explique l'expert. "Elle n'avait plus réellement de libre arbitre: elle a peur car son mari était toujours dans sa tête. Elle était toujours terrorisée et restait avec les diktats de son mari. L'emprise est permanente, pas seulement ... »</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="100" customHeight="1" s="61">
+      <c r="A48" s="85" t="n">
+        <v>3</v>
+      </c>
+      <c r="B48" s="86" t="inlineStr">
+        <is>
+          <t>📰 Article</t>
+        </is>
+      </c>
+      <c r="C48" s="86" t="inlineStr"/>
+      <c r="D48" s="85" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="E48" s="85" t="n">
         <v>14</v>
       </c>
-      <c r="F47" s="78" t="inlineStr">
+      <c r="F48" s="78" t="inlineStr">
         <is>
           <t>« ... « Soumise à l’emprise totalitaire de ce tyran domestique », qui l’a violée dès l’âge de 12-13 ans, quand il était son beau-père. Elle s’est « trouvée enfermée, emprisonnée dans l’emprise de son mari totalitaire ». Une emprise « dominante » et surtout « permanente », explique l’expert.
 Emprise permanente
@@ -2844,31 +2897,6 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="100" customHeight="1" s="61">
-      <c r="A48" s="85" t="n">
-        <v>3</v>
-      </c>
-      <c r="B48" s="86" t="inlineStr">
-        <is>
-          <t>📰 Article</t>
-        </is>
-      </c>
-      <c r="C48" s="86" t="inlineStr"/>
-      <c r="D48" s="85" t="inlineStr">
-        <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="E48" s="85" t="n">
-        <v>13</v>
-      </c>
-      <c r="F48" s="78" t="inlineStr">
-        <is>
-          <t>« Affaire Valérie Bacot: qu'est-ce que le "syndrome de la femme battue"?
-"Dans cet enfermement, elle n'avait pas d'autre échappatoire que de tuer son mari." Condamnée pour le meurtre de Daniel Polette, Valérie Bacot a toutefois été désignée par la cour d'assises comme la victime de cette affaire, à l'issue de son procès qui s'est achevé le 25 juin. Violée, battue et prostituée pendant des années, cette femme de 40 ans a réussi a démontrer la terreur dans laquelle elle vivait, sous l'emprise de cel ... »</t>
-        </is>
-      </c>
-    </row>
     <row r="49" ht="100" customHeight="1" s="61">
       <c r="A49" s="85" t="n">
         <v>4</v>
@@ -2881,7 +2909,7 @@
       <c r="C49" s="86" t="inlineStr"/>
       <c r="D49" s="85" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="E49" s="85" t="n">
@@ -2889,8 +2917,8 @@
       </c>
       <c r="F49" s="78" t="inlineStr">
         <is>
-          <t>« ... "Soumise à l'emprise totalitaire de ce tyran domestique" qui l'a violée dès l'âge de 12-13 ans quand il était alors son beau-père, Valérie Bacot n'a eu d'autre "possibilité que de détruire le sujet aliénant", a déclaré devant la cour d'assises de Saône-et-Loire Denis Prieur, expert psychiatre.
-Elle s'est "trouvée enfermée, emprisonnée dans l'emprise de son mari totalitaire". Une emprise "dominante" e ... »</t>
+          <t>« Affaire Valérie Bacot: qu'est-ce que le "syndrome de la femme battue"?
+"Dans cet enfermement, elle n'avait pas d'autre échappatoire que de tuer son mari." Condamnée pour le meurtre de Daniel Polette, Valérie Bacot a toutefois été désignée par la cour d'assises comme la victime de cette affaire, à l'issue de son procès qui s'est achevé le 25 juin. Violée, battue et prostituée pendant des années, cette femme de 40 ans a réussi a démontrer la terreur dans laquelle elle vivait, sous l'emprise de cel ... »</t>
         </is>
       </c>
     </row>
@@ -2900,25 +2928,22 @@
       </c>
       <c r="B50" s="86" t="inlineStr">
         <is>
-          <t>💬 Commentaire</t>
-        </is>
-      </c>
-      <c r="C50" s="86" t="inlineStr">
-        <is>
-          <t>YouTube — Victoria Charlton</t>
-        </is>
-      </c>
+          <t>📰 Article</t>
+        </is>
+      </c>
+      <c r="C50" s="86" t="inlineStr"/>
       <c r="D50" s="85" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="E50" s="85" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F50" s="78" t="inlineStr">
         <is>
-          <t>« le problème est que quelqu'un de battu a peur de déposé plainte car a peur des représailles. Le bourreau a une emprise que la personne battue pense être la cause car se croit la mauvaise personne qui énerve l'autre et a bien de la chance, qu'il reste car personne d'autre ne voudra d'elle... de grands manipulateurs ! »</t>
+          <t>« ... "Soumise à l'emprise totalitaire de ce tyran domestique" qui l'a violée dès l'âge de 12-13 ans quand il était alors son beau-père, Valérie Bacot n'a eu d'autre "possibilité que de détruire le sujet aliénant", a déclaré devant la cour d'assises de Saône-et-Loire Denis Prieur, expert psychiatre.
+Elle s'est "trouvée enfermée, emprisonnée dans l'emprise de son mari totalitaire". Une emprise "dominante" e ... »</t>
         </is>
       </c>
     </row>
@@ -2928,28 +2953,22 @@
       </c>
       <c r="B51" s="86" t="inlineStr">
         <is>
-          <t>💬 Commentaire</t>
-        </is>
-      </c>
-      <c r="C51" s="86" t="inlineStr">
-        <is>
-          <t>YouTube — Tibo InShape</t>
-        </is>
-      </c>
+          <t>📰 Article</t>
+        </is>
+      </c>
+      <c r="C51" s="86" t="inlineStr"/>
       <c r="D51" s="85" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="E51" s="85" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F51" s="78" t="inlineStr">
         <is>
-          <t>« Quel triste histoire, il ne faut pas avoir honte de votre geste ultime de survie !
-Une mort instantanée n’est rien comparé à des années de manipulation, souffrance et d’humiliation.
-Vous étiez sous l’emprise de ce monstre, vous avez garantie une vie meilleure à vos enfants par votre geste.
-J’espère, je souhaite de tout cœur, qu’avec le temps vous accepterait d’ouvrir les yeux et de voir la une super maman, la femme forte que vous êtes »</t>
+          <t>« ... u'il a peur pour elle."
+Dans son long texte, elle poursuit : "Je réagis comment quand mon fils a passé quasiment tout l'été chez mon frère parce qu'il a peur de rester à son propre domicile ? À part me dire de patienter ou de trouvez un travail c'est tout ce que l'on es capable de faire. J'ai un dossier en béton, mais apparemment en France, il faut être tué pour que l'on juge que c'était "une personne en danger". 24 800 viols en 2020 en France, 1 femme sur 3 dans le monde est victime de violence ... »</t>
         </is>
       </c>
     </row>
@@ -3059,9 +3078,37 @@
         </is>
       </c>
       <c r="E58" s="87" t="n">
+        <v>118</v>
+      </c>
+      <c r="F58" s="78" t="inlineStr">
+        <is>
+          <t>« ... "Pourquoi ce bois ?" "C'était le seul qu'on connaissait."
+"Comment étaient vos enfants ?
+-Ils ne savaient pas trop ce qu'ils faisaient..."
+12 h 55 : "Je me souviens juste d'avoir fermé les yeux"
+L'accusée raconte le tir mortel, mais sans jamais prononcer le mot concret. Après avoir raconté la violence de la passe avec le client, puis le retour de Daniel énervé dans la voiture, elle dit : "Je me souviens juste d'avoir fermé les yeux. Cette ode ... »</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="100" customHeight="1" s="61">
+      <c r="A59" s="87" t="n">
+        <v>4</v>
+      </c>
+      <c r="B59" s="88" t="inlineStr">
+        <is>
+          <t>📰 Article</t>
+        </is>
+      </c>
+      <c r="C59" s="88" t="inlineStr"/>
+      <c r="D59" s="87" t="inlineStr">
+        <is>
+          <t>2021-06-21</t>
+        </is>
+      </c>
+      <c r="E59" s="87" t="n">
         <v>114</v>
       </c>
-      <c r="F58" s="78" t="inlineStr">
+      <c r="F59" s="78" t="inlineStr">
         <is>
           <t>« ... "Pourquoi ce bois ?" "C'était le seul qu'on connaissait."
 "Comment étaient vos enfants ?
@@ -3071,83 +3118,59 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="100" customHeight="1" s="61">
-      <c r="A59" s="87" t="n">
-        <v>4</v>
-      </c>
-      <c r="B59" s="88" t="inlineStr">
+    <row r="60" ht="100" customHeight="1" s="61">
+      <c r="A60" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="B60" s="88" t="inlineStr">
         <is>
           <t>📰 Article</t>
         </is>
       </c>
-      <c r="C59" s="88" t="inlineStr"/>
-      <c r="D59" s="87" t="inlineStr">
+      <c r="C60" s="88" t="inlineStr"/>
+      <c r="D60" s="87" t="inlineStr">
         <is>
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="E59" s="87" t="n">
+      <c r="E60" s="87" t="n">
+        <v>109</v>
+      </c>
+      <c r="F60" s="78" t="inlineStr">
+        <is>
+          <t>« ... les petites briques qui construisent une personnalité sont fragilisées."
+Il parle de capacités de jugement "laminées".
+Les enfants Bacot ont été mangés par l'histoire de leurs parents
+Le Dr Prieur
+9 h 40 : "L'emprise devient totalitaire"
+Le psychiatre est invité à expliquer le syndrome de la femme battue. "Un modèle de couple pathologique,avec un sujet aliénant et l'autre aliéné, et ça va bien au-delà du caractère dominant, l'emprise est construite progressivement jusqu'à devenir totalitaire. L' ... »</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="100" customHeight="1" s="61">
+      <c r="A61" s="87" t="n">
+        <v>6</v>
+      </c>
+      <c r="B61" s="88" t="inlineStr">
+        <is>
+          <t>📰 Article</t>
+        </is>
+      </c>
+      <c r="C61" s="88" t="inlineStr"/>
+      <c r="D61" s="87" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="E61" s="87" t="n">
         <v>107</v>
       </c>
-      <c r="F59" s="78" t="inlineStr">
+      <c r="F61" s="78" t="inlineStr">
         <is>
           <t>« ... Les enfants Bacot ont été mangés par l'histoire de leurs parents
 Le Dr Prieur
 9 h 40 : "L'emprise devient totalitaire"
 Le psychiatre est invité à expliquer le syndrome de la femme battue. "Un modèle de couple pathologique,avec un sujet aliénant et l'autre aliéné, et ça va bien au-delà du caractère dominant, l'emprise est construite progressivement jusqu'à devenir totalitaire. L'aliéné devient l'objet de ... »</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="100" customHeight="1" s="61">
-      <c r="A60" s="87" t="n">
-        <v>5</v>
-      </c>
-      <c r="B60" s="88" t="inlineStr">
-        <is>
-          <t>📰 Article</t>
-        </is>
-      </c>
-      <c r="C60" s="88" t="inlineStr"/>
-      <c r="D60" s="87" t="inlineStr">
-        <is>
-          <t>2021-06-25</t>
-        </is>
-      </c>
-      <c r="E60" s="87" t="n">
-        <v>101</v>
-      </c>
-      <c r="F60" s="78" t="inlineStr">
-        <is>
-          <t>« ... 13 h 10 : "Ce n'est pas elle qui aurait dû se retrouver devant vous"
-Me Bonaggiunta plaide pour Valérie Bacot.
-"J'ai l'honneur de plaider pour Valérie Bacot et pour toutes ces femmes. Si je peux plaider, c'est qu'elle est vivante, qu'elle sortie des griffes de Daniel Polette. Ce n'est pas elle qui aurait dû se retrouver devant vous. C'est son violeur, son proxénète. Et tous ses complices. Les parents de Valérie, les institutions qui ... »</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="100" customHeight="1" s="61">
-      <c r="A61" s="87" t="n">
-        <v>6</v>
-      </c>
-      <c r="B61" s="88" t="inlineStr">
-        <is>
-          <t>📰 Article</t>
-        </is>
-      </c>
-      <c r="C61" s="88" t="inlineStr"/>
-      <c r="D61" s="87" t="inlineStr">
-        <is>
-          <t>2021-06-22</t>
-        </is>
-      </c>
-      <c r="E61" s="87" t="n">
-        <v>95</v>
-      </c>
-      <c r="F61" s="78" t="inlineStr">
-        <is>
-          <t>« ... général qui questionne Valérie Bacot."Aujourd'hui vous lisez les enseignements de votre thérapie ainsi : "Lucas a de l'emprise sur moi" ?" Réponse obscure de l'accusée.
-"Vous percevez que Lucas lui même a une vie compliquée et est un peu perdu ?", poursuit l'avocat général.
-Il recentre : "C'est le moment d'essayer de comprendre ce qui s'est passé à ce moment-là."
-Valérie Bacot explique être allée voir Lucas en premier après le crime car "c'était la logique d'aller vers quelqu'un qui savait ce qu ... »</t>
         </is>
       </c>
     </row>
@@ -3261,50 +3284,44 @@
       <c r="C67" s="90" t="inlineStr"/>
       <c r="D67" s="89" t="inlineStr">
         <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="E67" s="89" t="n">
+        <v>11</v>
+      </c>
+      <c r="F67" s="78" t="inlineStr">
+        <is>
+          <t>« ... Une histoire de crime dont on ne connaitra finalement pas trop les tenants et les aboutissants… Nous sommes à deux pas de la en Saône-et-Loire, en 1805. Mais que s’est-il passé ce jour-là sur les bords de la Loire ?
+Le
+Une histoire contemporaine qui va s’échelonner sur une trentaine d’années. Un homme issu d’une famille sans histoire. C’est dans la Nièvre que débute la carrière de gangster de notre homme.
+Le
+Une histoire con ... »</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="100" customHeight="1" s="61">
+      <c r="A68" s="89" t="n">
+        <v>3</v>
+      </c>
+      <c r="B68" s="90" t="inlineStr">
+        <is>
+          <t>📰 Article</t>
+        </is>
+      </c>
+      <c r="C68" s="90" t="inlineStr"/>
+      <c r="D68" s="89" t="inlineStr">
+        <is>
           <t>2021-06-23</t>
         </is>
       </c>
-      <c r="E67" s="89" t="n">
+      <c r="E68" s="89" t="n">
         <v>8</v>
       </c>
-      <c r="F67" s="78" t="inlineStr">
+      <c r="F68" s="78" t="inlineStr">
         <is>
           <t>« Procès Valérie Bacot : "C’est le symbole de ces femmes qu’on ne voit pas souffrir le martyre"
 Depuis lundi se tient le procès de Valérie Bacot au tribunal de Chalon-sur-Saône. Un procès largement médiatisé qui met en lumière la question des violences conjugales. Pendant 25 ans, Valérie Bacot a vécu l’enfer : violée dès l’âge de 12 ans par le compagnon de sa mère qui deviendra quelques années plus tard son mari, elle est isolée, battue et prostituée de force. En mars 2016, parce qu’elle a eu peur ... »</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="100" customHeight="1" s="61">
-      <c r="A68" s="89" t="n">
-        <v>3</v>
-      </c>
-      <c r="B68" s="90" t="inlineStr">
-        <is>
-          <t>💬 Commentaire</t>
-        </is>
-      </c>
-      <c r="C68" s="90" t="inlineStr">
-        <is>
-          <t>YouTube — Victoria Charlton</t>
-        </is>
-      </c>
-      <c r="D68" s="89" t="inlineStr">
-        <is>
-          <t>2021-02-16</t>
-        </is>
-      </c>
-      <c r="E68" s="89" t="n">
-        <v>5</v>
-      </c>
-      <c r="F68" s="78" t="inlineStr">
-        <is>
-          <t>« Wow, j'habite en France et je n'ai jamais entendu parler de cette affaire...
-2 ans pour un viol? Et il peut retourner auprès de sa victime?
-Elle a souffert toute sa vie, si justice lui avait été rendue à ce moment là, elle n'aurait pas eu à le faire elle même... 
-Je vais signer la pétition! 
-Merci beaucoup pour cette vidéo et ton sérieux! 
-Je commente pas souvent mais je vais essayer pour te soutenir un max! 
-A dimanche prochain ✌️ »</t>
         </is>
       </c>
     </row>
@@ -3314,27 +3331,23 @@
       </c>
       <c r="B69" s="90" t="inlineStr">
         <is>
-          <t>💬 Commentaire</t>
-        </is>
-      </c>
-      <c r="C69" s="90" t="inlineStr">
-        <is>
-          <t>YouTube — Canal Crime</t>
-        </is>
-      </c>
+          <t>📰 Article</t>
+        </is>
+      </c>
+      <c r="C69" s="90" t="inlineStr"/>
       <c r="D69" s="89" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2022-07-08</t>
         </is>
       </c>
       <c r="E69" s="89" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F69" s="78" t="inlineStr">
         <is>
-          <t>« Bon documentaire sur une histoire sordide mais Madame la voix off (IA ou pas ?), aux Assises, il n’y a pas de Procureur mais un Avocat General qui demande une peine au nom de la société.
-On ne se fait pas justice soi-même, heureusement et dans cette affaire, elle a très bien fait son travail, auparavant, certainement pas (autoriser qu’une mère emmène sa fille voir son violeur est inadmissible, recevoir des lettres de ce même violeur est incompréhensible).
-Par contre, il est certain que Valérie B ... »</t>
+          <t>« Télévision Un documentaire sur l'affaire Valérie Bacot ce soir sur RMC Story
+Un documentaire retraçant l'affaire Valérie Bacot est diffusée ce vendredi soir 8 juillet, sur la chaîne RMC Story.
+Valérie Bacot a été condamnée par les assises de Saône-et-Loire à Chalon-sur-Saône en juin 2021 à 4 ans de prison dont 3 ans avec sursis, pour avoir assassiné son mari violent en 2016 dans le Brionnais. Elle avait ensuite fait disparaître le corps avec l'aide de ses enfants en l'enterrant près du château d ... »</t>
         </is>
       </c>
     </row>
@@ -3349,24 +3362,20 @@
       </c>
       <c r="C70" s="90" t="inlineStr">
         <is>
-          <t>YouTube — Bercrimes</t>
+          <t>YouTube — BFMTV</t>
         </is>
       </c>
       <c r="D70" s="89" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-12-03</t>
         </is>
       </c>
       <c r="E70" s="89" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F70" s="78" t="inlineStr">
         <is>
-          <t>« Encore une fois une histoire sordide ou la manipulation avait pris au piège une enfant devenue femme
-Dans cette histoire il est important qu'elle parle devant la justice en espérant que cette justice cette fois ci écoute une personne qui sous l'emprise la peur en est arrivé à tuer
-Je n'excuse en rien son acte mais il est important de regarder le contexte de l'histoire
-J'espère qu'elle sera entendu et que cette justice soit juste
-Je lui souhaite de réussir à tourner la page »</t>
+          <t>« ... rigine d’une maladie, on en reconnaît les symptômes puis on en recherche la cause pour déterminer si oui ou non le mal est curable et enfin on applique le traitement final. C’est ça, le RANDORI : RAN la tempête… la tempête du randori est en fait une métaphore de nos vies de souffrance. Alors que Madame soit « hystérique », que Monsieur soit « alcoolisé », sur Madame ait le nez cassé et Monsieur un œil au beurre noir, que Madame ait dit à Monsieur que leur histoire d’amour est finie ou que Monsie ... »</t>
         </is>
       </c>
     </row>
@@ -3381,20 +3390,21 @@
       </c>
       <c r="C71" s="90" t="inlineStr">
         <is>
-          <t>YouTube — Canal Crime</t>
+          <t>YouTube — AJ+ français</t>
         </is>
       </c>
       <c r="D71" s="89" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E71" s="89" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F71" s="78" t="inlineStr">
         <is>
-          <t>« Cette histoire me fait penser à un film l emprise avec fred testot. Tiré d une vraie histoire est ce que c est la même histoire »</t>
+          <t>« ... leur sauce en fonction des goûts de leur audience et de ce qui va faire parler, comme dans le cas de ces vidéos. Moi, je fais un simple constat que je partage dans les commentaires, en me basant sur ce que j’ai vu, que tu peux vérifier par toi-même, et que tu aurais dû faire avant de faire cette comparaison stupide
+Et pour info, on ne devient pas incel en regardant des vidéos ou des films à but humoristique, le génie. Le type était déjà comme ça, et ce genre de vidéos est redevenu populaire réc ... »</t>
         </is>
       </c>
     </row>
@@ -3522,77 +3532,83 @@
       </c>
       <c r="B79" s="92" t="inlineStr">
         <is>
+          <t>💬 Commentaire</t>
+        </is>
+      </c>
+      <c r="C79" s="92" t="inlineStr">
+        <is>
+          <t>YouTube — Ça commence aujourd'hui - Fran</t>
+        </is>
+      </c>
+      <c r="D79" s="91" t="inlineStr">
+        <is>
+          <t>2019-09-01</t>
+        </is>
+      </c>
+      <c r="E79" s="91" t="n">
+        <v>21</v>
+      </c>
+      <c r="F79" s="78" t="inlineStr">
+        <is>
+          <t>« ... peine de licenciement  pour faute. 
+ensuite comme l'attaque informatique par 3 fois   l'a mis au chômage   il a menacé de mort une  amie de sa femme,    et mis le feu à la maison commune.   acte criminel .   et peine de 1 an sur l'incendie.   et elle avait des contrôles judiciaires pour la protéger  elle,   des délits et crime de son ex.    et c’était des déclarations à la justice  des déplacements non quotidiens.   Mais la justice ... »</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="100" customHeight="1" s="61">
+      <c r="A80" s="91" t="n">
+        <v>5</v>
+      </c>
+      <c r="B80" s="92" t="inlineStr">
+        <is>
+          <t>💬 Commentaire</t>
+        </is>
+      </c>
+      <c r="C80" s="92" t="inlineStr">
+        <is>
+          <t>YouTube — Pluriel</t>
+        </is>
+      </c>
+      <c r="D80" s="91" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="E80" s="91" t="n">
+        <v>21</v>
+      </c>
+      <c r="F80" s="78" t="inlineStr">
+        <is>
+          <t>« choix de laisser les gens dans l'ignorance, ce n'est pas mon choix, je ne vous demande pas de faire comme moi, pas plus que je cherche à faire comme vous. Si on vous écoutes, les Messagers de Dieu, les prédicateurs qui les ont suivi sont en tords d'avoir prodiguer des conseils à leurs entourages, d'avoir inciter les gens à croire. C'est vous qui êtes de mauvaise foi. Nulle part mon commentaire a pour objectif de culpabiliser les gens, est-ce que c'est forcément la faute des gens d'être ignorant ... »</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="100" customHeight="1" s="61">
+      <c r="A81" s="91" t="n">
+        <v>6</v>
+      </c>
+      <c r="B81" s="92" t="inlineStr">
+        <is>
           <t>📰 Article</t>
         </is>
       </c>
-      <c r="C79" s="92" t="inlineStr"/>
-      <c r="D79" s="91" t="inlineStr">
+      <c r="C81" s="92" t="inlineStr"/>
+      <c r="D81" s="91" t="inlineStr">
         <is>
           <t>2021-06-25</t>
         </is>
       </c>
-      <c r="E79" s="91" t="n">
+      <c r="E81" s="91" t="n">
         <v>20</v>
       </c>
-      <c r="F79" s="78" t="inlineStr">
+      <c r="F81" s="78" t="inlineStr">
         <is>
           <t>« ... Tout le monde est encore à l'intérieur de la salle.
 20 h 19 : le verdict est rendu
 Valérie Bacot est déclarée coupable d'assassinat. La préméditation est retenue.
 Valérie Bacot est condamnée à quatre ans de prison, dont trois ans avec sursis probatoire et obligation de soins pendant trois ans. Elle ne sera pas incarcérée à nouveau.
 Une partie du public a applaudi lorsque la présidente a expliqué à Valérie Bacot qu'elle sortirait libre du palais de justice.
-La peine prononcée est inf ... »</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="100" customHeight="1" s="61">
-      <c r="A80" s="91" t="n">
-        <v>5</v>
-      </c>
-      <c r="B80" s="92" t="inlineStr">
-        <is>
-          <t>📰 Article</t>
-        </is>
-      </c>
-      <c r="C80" s="92" t="inlineStr"/>
-      <c r="D80" s="91" t="inlineStr">
-        <is>
-          <t>2016-03-24</t>
-        </is>
-      </c>
-      <c r="E80" s="91" t="n">
-        <v>18</v>
-      </c>
-      <c r="F80" s="78" t="inlineStr">
-        <is>
-          <t>« Elle a été condamnée, ce jeudi 24 mars par la cour d’assise de Nancy (Meurthe-et-Moselle) à 9 ans de prison pour le meurtre de son mari, en 2012. Une peine clémente, malgré une défense défaillante.
-C’est un procès complexe qui s’achève aux assises de Nancy, ce jeudi 24 mars. Au terme de quatre jours de débats menés avec justesse et finesse par la présidente Catherine Hologne, la cour a finalement décidé de condamner Sylvi ... »</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="100" customHeight="1" s="61">
-      <c r="A81" s="91" t="n">
-        <v>6</v>
-      </c>
-      <c r="B81" s="92" t="inlineStr">
-        <is>
-          <t>📰 Article</t>
-        </is>
-      </c>
-      <c r="C81" s="92" t="inlineStr"/>
-      <c r="D81" s="91" t="inlineStr">
-        <is>
-          <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="E81" s="91" t="n">
-        <v>14</v>
-      </c>
-      <c r="F81" s="78" t="inlineStr">
-        <is>
-          <t>« Procès de Valérie Bacot : pour ses avocates c'est un "verdict de clémence" qui "fera date"
-Selon les avocats de Valérie Bacot, condamnée vendredi 25 juin à quatre ans de prison dont trois avec sursis, mais ressortie libre du tribunal, il s'agit d'un "verdict de clémence" qui "fera date".
-Me Janine Bonaggiunta et Nathalie Tomasini, les avocats de Valérie Bacot expliquent au micro de France 3 Bourgogne-Franche Comté que cette condamnation est "moins sévère" que ce que Valérie Bacot pensait. Elle é ... »</t>
+La peine prononcée ... »</t>
         </is>
       </c>
     </row>
